--- a/Archivos/CONFIGURACION/Formulas.xlsx
+++ b/Archivos/CONFIGURACION/Formulas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Procesos_Uipath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\CONFIGURACION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F7146CF-5C54-450B-B8AD-BB04E57337CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCF3FBD-4999-4008-B5B8-81945F84516A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,7 +111,7 @@
     <t>=IF(OR(M_VALUE_DINAMIC_="SÍ", AND(X_VALUE_DINAMIC_&lt;&gt;"", X_VALUE_DINAMIC_&lt;=8), AND(Y_VALUE_DINAMIC_&lt;&gt;"", Y_VALUE_DINAMIC_&lt;=8), AND(Z_VALUE_DINAMIC_&lt;&gt;"", Z_VALUE_DINAMIC_&lt;=8), AND(Q_VALUE_DINAMIC_&lt;&gt;"", Q_VALUE_DINAMIC_&lt;=3), AND(AD_VALUE_DINAMIC_&lt;&gt;"", AD_VALUE_DINAMIC_&lt;=8), AND(AE4&lt;&gt;"", AE4&lt;=8),AND(N_VALUE_DINAMIC_&lt;&gt;"", N_VALUE_DINAMIC_&lt;=8)), "Alerta", "Correcto")</t>
   </si>
   <si>
-    <t>=CONCATENATE("?gid=",BC1,"#gid=",BC1,"&amp;range=A",ROW())</t>
+    <t>=CONCATENATE("?gid=",BB$1,"#gid=",$BB$1,"&amp;range=A",ROW())</t>
   </si>
 </sst>
 </file>

--- a/Archivos/CONFIGURACION/Formulas.xlsx
+++ b/Archivos/CONFIGURACION/Formulas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Procesos_Uipath\541_DISPOINFOMEDALIABRYAM_NF_SEG_SEG\Archivos\CONFIGURACION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCF3FBD-4999-4008-B5B8-81945F84516A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D100B6-7836-4452-BF7A-1F5DB1B1FE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>INDEX_COLUMN</t>
   </si>
@@ -105,13 +105,16 @@
     <t>BE</t>
   </si>
   <si>
-    <t>AW</t>
-  </si>
-  <si>
     <t>=IF(OR(M_VALUE_DINAMIC_="SÍ", AND(X_VALUE_DINAMIC_&lt;&gt;"", X_VALUE_DINAMIC_&lt;=8), AND(Y_VALUE_DINAMIC_&lt;&gt;"", Y_VALUE_DINAMIC_&lt;=8), AND(Z_VALUE_DINAMIC_&lt;&gt;"", Z_VALUE_DINAMIC_&lt;=8), AND(Q_VALUE_DINAMIC_&lt;&gt;"", Q_VALUE_DINAMIC_&lt;=3), AND(AD_VALUE_DINAMIC_&lt;&gt;"", AD_VALUE_DINAMIC_&lt;=8), AND(AE4&lt;&gt;"", AE4&lt;=8),AND(N_VALUE_DINAMIC_&lt;&gt;"", N_VALUE_DINAMIC_&lt;=8)), "Alerta", "Correcto")</t>
   </si>
   <si>
     <t>=CONCATENATE("?gid=",BB$1,"#gid=",$BB$1,"&amp;range=A",ROW())</t>
+  </si>
+  <si>
+    <t>=IF(AM_VALUE_DINAMIC_="Comentarios positivos", "Positivo",IF(AM_VALUE_DINAMIC_="Sin comentario","Sin comentario"))</t>
+  </si>
+  <si>
+    <t>AN</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
@@ -489,10 +492,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -506,7 +509,7 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
@@ -520,7 +523,7 @@
         <v>19</v>
       </c>
       <c r="B6">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
@@ -534,7 +537,7 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -548,7 +551,7 @@
         <v>20</v>
       </c>
       <c r="B8">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -562,10 +565,10 @@
         <v>21</v>
       </c>
       <c r="B9">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -576,12 +579,26 @@
         <v>17</v>
       </c>
       <c r="B10">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>39</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
         <v>7</v>
       </c>
     </row>
